--- a/asx_eod_output/Report_XLSX/Report_20260807.xlsx
+++ b/asx_eod_output/Report_XLSX/Report_20260807.xlsx
@@ -488,24 +488,24 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.5</v>
+        <v>1.502</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.035</v>
+        <v>0.037</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>2.53%</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
         <v>153181</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>229771.5</v>
+        <v>230077.86</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>5361.33</v>
+        <v>5667.7</v>
       </c>
     </row>
     <row r="5">
@@ -515,24 +515,24 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2.385</v>
+        <v>2.41</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.075</v>
+        <v>0.1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.25%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
         <v>70000</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>166950</v>
+        <v>168700</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>5250</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="6">
@@ -569,24 +569,24 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>62.84</v>
+        <v>62.87</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.08%</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
         <v>11065</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>695324.6</v>
+        <v>695656.55</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>221.3</v>
+        <v>553.25</v>
       </c>
     </row>
     <row r="8">
@@ -623,14 +623,14 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>177.66</v>
+        <v>177.31</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-2.21</v>
+        <v>-2.56</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>-1.42%</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
@@ -677,24 +677,24 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>131.62</v>
+        <v>131.91</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-0.74</v>
+        <v>-0.45</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-0.34%</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
         <v>4000</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>526480</v>
+        <v>527640</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2960</v>
+        <v>-1800</v>
       </c>
     </row>
     <row r="12">
@@ -812,14 +812,14 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>37.93</v>
+        <v>37.94</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-0.6</v>
+        <v>-0.59</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-1.56%</t>
+          <t>-1.53%</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
@@ -870,10 +870,10 @@
       <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr"/>
       <c r="F18" s="8" t="n">
-        <v>1733758.06</v>
+        <v>1737306.37</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>5832.03</v>
+        <v>9380.34</v>
       </c>
     </row>
   </sheetData>

--- a/asx_eod_output/Report_XLSX/Report_20260807.xlsx
+++ b/asx_eod_output/Report_XLSX/Report_20260807.xlsx
@@ -488,24 +488,24 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.502</v>
+        <v>1.537</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.037</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>4.91%</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
         <v>153181</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>230077.86</v>
+        <v>235439.2</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>5667.7</v>
+        <v>11029.03</v>
       </c>
     </row>
     <row r="5">
@@ -515,24 +515,24 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2.41</v>
+        <v>2.435</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.1</v>
+        <v>0.125</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>5.41%</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
         <v>70000</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>168700</v>
+        <v>170450</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>7000</v>
+        <v>8750</v>
       </c>
     </row>
     <row r="6">
@@ -542,24 +542,24 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1.12</v>
+        <v>1.105</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.21%</t>
+          <t>6.76%</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
         <v>57458</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>64352.96</v>
+        <v>63491.09</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>4883.93</v>
+        <v>4022.06</v>
       </c>
     </row>
     <row r="7">
@@ -569,24 +569,24 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>62.87</v>
+        <v>63.04</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.05</v>
+        <v>0.22</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
         <v>11065</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>695656.55</v>
+        <v>697537.6</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>553.25</v>
+        <v>2434.3</v>
       </c>
     </row>
     <row r="8">
@@ -623,14 +623,14 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>177.31</v>
+        <v>177.9</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-2.56</v>
+        <v>-1.97</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-1.42%</t>
+          <t>-1.10%</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
@@ -650,24 +650,24 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.87</v>
+        <v>0.875</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0.025</v>
+        <v>0.03</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.96%</t>
+          <t>3.55%</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
         <v>10000</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>8700</v>
+        <v>8750</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
     </row>
     <row r="11">
@@ -677,24 +677,24 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>131.91</v>
+        <v>131.89</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-0.45</v>
+        <v>-0.47</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
         <v>4000</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>527640</v>
+        <v>527560</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1800</v>
+        <v>-1880</v>
       </c>
     </row>
     <row r="12">
@@ -704,24 +704,24 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>-0.275</v>
+        <v>-0.005</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-100.00%</t>
+          <t>-1.82%</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
         <v>20000</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-5500</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="13">
@@ -758,24 +758,24 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0.091</v>
+        <v>0.092</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-1.09%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
         <v>9412</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>856.49</v>
+        <v>865.9</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-9.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -812,14 +812,14 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>37.94</v>
+        <v>37.97</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-0.59</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-1.53%</t>
+          <t>-1.45%</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
@@ -839,24 +839,24 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>31.98</v>
+        <v>31.975</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.26</v>
+        <v>0.255</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.80%</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
         <v>1288</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>41190.24</v>
+        <v>41183.8</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>334.88</v>
+        <v>328.44</v>
       </c>
     </row>
     <row r="18">
@@ -870,10 +870,10 @@
       <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr"/>
       <c r="F18" s="8" t="n">
-        <v>1737306.37</v>
+        <v>1750809.86</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>9380.34</v>
+        <v>22883.83</v>
       </c>
     </row>
   </sheetData>

--- a/asx_eod_output/Report_XLSX/Report_20260807.xlsx
+++ b/asx_eod_output/Report_XLSX/Report_20260807.xlsx
@@ -488,24 +488,24 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.537</v>
+        <v>1.535</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.91%</t>
+          <t>4.78%</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
         <v>153181</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>235439.2</v>
+        <v>235132.83</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>11029.03</v>
+        <v>10722.67</v>
       </c>
     </row>
     <row r="5">
@@ -515,24 +515,24 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2.435</v>
+        <v>2.42</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.125</v>
+        <v>0.11</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.41%</t>
+          <t>4.76%</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
         <v>70000</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>170450</v>
+        <v>169400</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>8750</v>
+        <v>7700</v>
       </c>
     </row>
     <row r="6">
@@ -542,24 +542,24 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1.105</v>
+        <v>1.11</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6.76%</t>
+          <t>7.25%</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
         <v>57458</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>63491.09</v>
+        <v>63778.38</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>4022.06</v>
+        <v>4309.35</v>
       </c>
     </row>
     <row r="7">
@@ -569,24 +569,24 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>63.04</v>
+        <v>62.97</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.24%</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
         <v>11065</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>697537.6</v>
+        <v>696763.05</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2434.3</v>
+        <v>1659.75</v>
       </c>
     </row>
     <row r="8">
@@ -623,14 +623,14 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>177.9</v>
+        <v>178.01</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-1.97</v>
+        <v>-1.86</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-1.10%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
@@ -650,24 +650,24 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.875</v>
+        <v>0.87</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.55%</t>
+          <t>2.96%</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
         <v>10000</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>8750</v>
+        <v>8700</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -677,24 +677,24 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>131.89</v>
+        <v>132.19</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-0.47</v>
+        <v>-0.17</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.36%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
         <v>4000</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>527560</v>
+        <v>528760</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1880</v>
+        <v>-680</v>
       </c>
     </row>
     <row r="12">
@@ -704,24 +704,24 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>-0.005</v>
+        <v>0.005</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>1.82%</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
         <v>20000</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>5400</v>
+        <v>5600</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-100</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -812,14 +812,14 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>37.97</v>
+        <v>37.93</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>-1.56%</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
@@ -839,24 +839,24 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>31.975</v>
+        <v>31.88</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.255</v>
+        <v>0.16</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
         <v>1288</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>41183.8</v>
+        <v>41061.44</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>328.44</v>
+        <v>206.08</v>
       </c>
     </row>
     <row r="18">
@@ -870,10 +870,10 @@
       <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr"/>
       <c r="F18" s="8" t="n">
-        <v>1750809.86</v>
+        <v>1750193.88</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>22883.83</v>
+        <v>22267.85</v>
       </c>
     </row>
   </sheetData>
